--- a/KLCN021_API_Catalog.xlsx
+++ b/KLCN021_API_Catalog.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conventions" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'API Catalog'!$A$1:$I$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'API Catalog'!$A$1:$J$126</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -79,7 +79,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -89,6 +89,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -454,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I89"/>
+  <dimension ref="A1:J126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="6" customWidth="1" style="4" min="1" max="1"/>
@@ -466,6 +469,7 @@
     <col width="38" customWidth="1" style="4" min="7" max="7"/>
     <col width="30" customWidth="1" style="4" min="8" max="8"/>
     <col width="32" customWidth="1" style="4" min="9" max="9"/>
+    <col width="36" customWidth="1" style="4" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="4">
@@ -514,6 +518,11 @@
           <t>Mã lỗi/Ghi chú</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Trạng thái triển khai</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -559,6 +568,11 @@
           <t>409 email đã tồn tại</t>
         </is>
       </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -604,6 +618,11 @@
           <t>All failures logged; default5 wrong passwords lock15min. Config Authentication:MaxFailedAttempts/LockoutMinutes. Unauthorized401.</t>
         </is>
       </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -649,6 +668,11 @@
           <t>Inactive or temporarily locked account401.</t>
         </is>
       </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -694,6 +718,11 @@
           <t>Only caller-owned refresh token revoked.</t>
         </is>
       </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -735,6 +764,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -776,6 +810,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -817,6 +856,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -858,6 +902,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -899,6 +948,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -940,6 +994,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -985,6 +1044,11 @@
           <t>404 không tồn tại</t>
         </is>
       </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1030,6 +1094,11 @@
           <t>409 đang được sử dụng</t>
         </is>
       </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1052,7 +1121,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>List staff for customer booking</t>
+          <t>Nhân viên cho quản trị và chọn lịch</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1067,12 +1136,17 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>[{ nhanVienId, hoTen, chucVu, chuyenMon, soDienThoai, ngayVaoLam }]</t>
+          <t>[{nhanVienId,hoTen,chucVu,chuyenMon,soDienThoai,ngayVaoLam,taiKhoanId}]</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Authenticated; GET access expanded only. Writes/schedules remain Admin/Manager.</t>
+          <t>taiKhoanId chỉ cho quản trị, Customer nhận null; không trả mật khẩu.</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
         </is>
       </c>
     </row>
@@ -1097,25 +1171,34 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Tạo nhân viên</t>
+          <t>Tạo nhân viên kèm tài khoản Staff</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>STAFF.WRITE</t>
+          <t>Admin/Manager/Reception + STAFF.WRITE</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>hoTen, chucVu, chuyenMon, soDienThoai</t>
+          <t>fullName, position?, specialty?, phone?, hireDate?, email, password (8–128)</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>NhanVienDto</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="n"/>
+          <t>201 {nhanVienId,taiKhoanId,hoTen,chucVu,chuyenMon,soDienThoai,ngayVaoLam}</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Transaction account+employee+audit; hash password; 400 dữ liệu sai, 409 email trùng.</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1161,6 +1244,11 @@
           <t>Finite detail projection; no EF back references. 404 missing.</t>
         </is>
       </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1183,25 +1271,34 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Cập nhật nhân viên</t>
+          <t>Sửa hồ sơ nhân viên</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>STAFF.WRITE</t>
+          <t>Admin/Manager/Reception + STAFF.WRITE</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>NhanVien fields</t>
+          <t>fullName, position?, specialty?, phone?, hireDate?</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>NhanVienDto</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="n"/>
+          <t>Employee fields</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Không thay đổi thông tin đăng nhập.</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1247,6 +1344,11 @@
           <t>409 if any appointment/schedule references staff, including cancelled history.</t>
         </is>
       </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1288,6 +1390,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1333,6 +1440,11 @@
           <t>409 trùng ca</t>
         </is>
       </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1374,6 +1486,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n"/>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -1415,6 +1532,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -1456,6 +1578,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n"/>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -1497,6 +1624,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -1538,6 +1670,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n"/>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -1579,6 +1716,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n"/>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -1620,6 +1762,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n"/>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -1661,6 +1808,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n"/>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -1702,6 +1854,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -1743,6 +1900,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -1784,6 +1946,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n"/>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="25" customHeight="1" s="4">
       <c r="A32" s="2" t="n">
@@ -1825,6 +1992,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -1866,6 +2038,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -1907,6 +2084,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -1948,6 +2130,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n"/>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -1989,6 +2176,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n"/>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -2030,6 +2222,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n"/>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -2071,6 +2268,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n"/>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -2112,6 +2314,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n"/>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -2153,6 +2360,11 @@
         </is>
       </c>
       <c r="I40" s="2" t="n"/>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -2198,6 +2410,11 @@
           <t>Individual candidate slots every30minutes; full duration must fit shift and avoid busy intervals; service duration overrides durationMinutes. Alias available-slots. 400 invalid input.</t>
         </is>
       </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -2243,6 +2460,11 @@
           <t>Catalog-derived expectedPrice; complete active combo composition/date required. Management also APPOINTMENT.WRITE. Invalid service/combo/shift400; overlap409.</t>
         </is>
       </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -2288,6 +2510,11 @@
           <t>Management APPOINTMENT.READ sees all; Staff APPOINTMENT.READ assigned only; Customer own records.</t>
         </is>
       </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -2333,6 +2560,11 @@
           <t>403 other customer; 404 missing; no EF back references.</t>
         </is>
       </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -2378,6 +2610,11 @@
           <t>409 chuyển trạng thái không hợp lệ</t>
         </is>
       </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -2419,6 +2656,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n"/>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -2464,6 +2706,11 @@
           <t>409 unless pending/confirmed or if intervals overlap; 400 invalid time/staff or outside selected staff shift.</t>
         </is>
       </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -2509,6 +2756,11 @@
           <t>204 only for ChoXacNhan/DaXacNhan/DaDen. 409 otherwise; 403 other customer; 404 missing.</t>
         </is>
       </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -2554,6 +2806,11 @@
           <t>Completed/matching booked lines required. Whole redeemed points clamp to actual discount; ledger references invoice. Management also INVOICE.WRITE.</t>
         </is>
       </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -2599,6 +2856,11 @@
           <t>Staff see all; customer own only.</t>
         </is>
       </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -2640,6 +2902,11 @@
         </is>
       </c>
       <c r="I51" s="2" t="n"/>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -2681,6 +2948,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n"/>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -2722,6 +2994,11 @@
         </is>
       </c>
       <c r="I53" s="2" t="n"/>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -2767,6 +3044,11 @@
           <t>Customer403; repeated409; zero-total settles without payment row or earned points.</t>
         </is>
       </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -2808,6 +3090,11 @@
         </is>
       </c>
       <c r="I55" s="2" t="n"/>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -2849,6 +3136,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n"/>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -2890,6 +3182,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n"/>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -2931,6 +3228,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n"/>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -2976,6 +3278,11 @@
           <t>discountType: PhanTram (0..100) or SoTien (&gt;=0); normalized; valid date interval required.</t>
         </is>
       </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -3017,6 +3324,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n"/>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -3058,6 +3370,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n"/>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="25" customHeight="1" s="4">
       <c r="A62" s="2" t="n">
@@ -3099,6 +3416,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n"/>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
@@ -3144,6 +3466,11 @@
           <t>Same validation as create: normalized unique code, valid promotion/customer, future expiry, nonnegative amount. 400 invalid;409 duplicate.</t>
         </is>
       </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -3185,6 +3512,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n"/>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -3226,6 +3558,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n"/>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -3267,6 +3604,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n"/>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
@@ -3308,6 +3650,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n"/>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -3349,6 +3696,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n"/>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
@@ -3390,6 +3742,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n"/>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -3431,6 +3788,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n"/>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
@@ -3472,6 +3834,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n"/>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
@@ -3513,6 +3880,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n"/>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
@@ -3554,6 +3926,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n"/>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
@@ -3595,6 +3972,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n"/>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
@@ -3636,6 +4018,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n"/>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
@@ -3677,6 +4064,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n"/>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
@@ -3718,6 +4110,11 @@
         </is>
       </c>
       <c r="I77" s="2" t="n"/>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
@@ -3759,6 +4156,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n"/>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
@@ -3804,6 +4206,11 @@
           <t>state không hợp lệ: 400</t>
         </is>
       </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
@@ -3845,6 +4252,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n"/>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
@@ -3890,6 +4302,11 @@
           <t>Không cho hủy liên kết cuối cùng</t>
         </is>
       </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
@@ -3935,6 +4352,11 @@
           <t>Nên giới hạn Admin/Security</t>
         </is>
       </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
@@ -3976,6 +4398,11 @@
         </is>
       </c>
       <c r="I83" s="2" t="n"/>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
@@ -4017,6 +4444,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n"/>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
@@ -4058,6 +4490,11 @@
         </is>
       </c>
       <c r="I85" s="2" t="n"/>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>Chưa có trong Swagger hiện tại</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
@@ -4103,144 +4540,2014 @@
           <t>403 wrong owner; 400 invalid time/staff or outside selected shift; 404 missing; 409 unless pending/confirmed or interval overlap.</t>
         </is>
       </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" t="n">
+      <c r="A87" s="5" t="n">
         <v>86</v>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="5" t="inlineStr">
         <is>
           <t>Staff</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C87" s="5" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D87" s="5" t="inlineStr">
         <is>
           <t>/api/v1/staff/me/appointments</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="E87" s="5" t="inlineStr">
         <is>
           <t>Own assigned appointments</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F87" s="5" t="inlineStr">
         <is>
           <t>Staff + APPOINTMENT.READ</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="G87" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="H87" s="5" t="inlineStr">
         <is>
           <t>Array of assigned appointment summaries</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>Staff profile missing returns []; no other employee records.</t>
+      <c r="I87" s="5" t="inlineStr">
+        <is>
+          <t>403 nếu chưa có hồ sơ; chỉ dữ liệu được phân công cho hồ sơ liên kết tài khoản.</t>
+        </is>
+      </c>
+      <c r="J87" s="5" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="n">
+      <c r="A88" s="5" t="n">
         <v>87</v>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B88" s="5" t="inlineStr">
         <is>
           <t>Staff</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C88" s="5" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D88" s="5" t="inlineStr">
         <is>
           <t>/api/v1/staff/me/schedules</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="E88" s="5" t="inlineStr">
         <is>
           <t>Own work schedules</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="F88" s="5" t="inlineStr">
         <is>
           <t>Staff + STAFF.READ</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="G88" s="5" t="inlineStr">
         <is>
           <t>from?, to?</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="H88" s="5" t="inlineStr">
         <is>
           <t>Array of own schedule summaries</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>Staff profile missing returns []; no other employee records.</t>
+      <c r="I88" s="5" t="inlineStr">
+        <is>
+          <t>403 nếu chưa có hồ sơ; chỉ dữ liệu được phân công cho hồ sơ liên kết tài khoản.</t>
+        </is>
+      </c>
+      <c r="J88" s="5" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="n">
+      <c r="A89" s="5" t="n">
         <v>88</v>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B89" s="5" t="inlineStr">
         <is>
           <t>Reviews</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C89" s="5" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D89" s="5" t="inlineStr">
         <is>
           <t>/api/v1/reviews/pending</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="E89" s="5" t="inlineStr">
         <is>
           <t>Reviews awaiting moderation</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F89" s="5" t="inlineStr">
         <is>
           <t>Admin/Manager + REVIEW.MODERATE</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="G89" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="H89" s="5" t="inlineStr">
         <is>
           <t>Review summary[] (latest200)</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="I89" s="5" t="inlineStr">
         <is>
           <t>Public GET reviews remains visible reviews only.</t>
         </is>
       </c>
+      <c r="J89" s="5" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>Accounts</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/admin/accounts</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>Tạo tài khoản và hồ sơ liên kết</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>Admin + ACCOUNT.WRITE</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr">
+        <is>
+          <t>email, password, fullName, phone?, roleId, staffId?</t>
+        </is>
+      </c>
+      <c r="H90" s="5" t="inlineStr">
+        <is>
+          <t>201 AdminAccountResponse</t>
+        </is>
+      </c>
+      <c r="I90" s="5" t="inlineStr">
+        <is>
+          <t>staffId chỉ cho Staff; 409 email hoặc hồ sơ đã có tài khoản.</t>
+        </is>
+      </c>
+      <c r="J90" s="5" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>Accounts</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>PATCH</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/admin/accounts/{id}/role</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>Gán vai trò/liên kết nhân viên</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>Admin + ACCOUNT.WRITE</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>roleId, staffId?</t>
+        </is>
+      </c>
+      <c r="H91" s="5" t="inlineStr">
+        <is>
+          <t>200 AdminAccountResponse</t>
+        </is>
+      </c>
+      <c r="I91" s="5" t="inlineStr">
+        <is>
+          <t>Giữ role Staff và đổi hồ sơ cũ chưa có lịch/ca; giữ lịch của hồ sơ chọn, revoke refresh và audit.</t>
+        </is>
+      </c>
+      <c r="J91" s="5" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/auth/permissions</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>Quyền hiện tại của tài khoản</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>Authenticated</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H92" s="5" t="inlineStr">
+        <is>
+          <t>{role,permissions[]}</t>
+        </is>
+      </c>
+      <c r="I92" s="5" t="inlineStr">
+        <is>
+          <t>Chỉ quyền được cấp và đang hoạt động trong database.</t>
+        </is>
+      </c>
+      <c r="J92" s="5" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>Combos</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/combos/{id}</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>Endpoint triển khai trong Swagger</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>Theo vai trò, quyền và phạm vi dữ liệu tại API</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H93" s="5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I93" s="5" t="inlineStr">
+        <is>
+          <t>Xem Swagger/controller để biết DTO và điều kiện chi tiết.</t>
+        </is>
+      </c>
+      <c r="J93" s="5" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>Promotions</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/promotions/vouchers/{id}</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>Endpoint triển khai trong Swagger</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="inlineStr">
+        <is>
+          <t>Theo vai trò, quyền và phạm vi dữ liệu tại API</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H94" s="5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I94" s="5" t="inlineStr">
+        <is>
+          <t>Xem Swagger/controller để biết DTO và điều kiện chi tiết.</t>
+        </is>
+      </c>
+      <c r="J94" s="5" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>Promotions</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/promotions/{id}</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>Endpoint triển khai trong Swagger</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="inlineStr">
+        <is>
+          <t>Theo vai trò, quyền và phạm vi dữ liệu tại API</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H95" s="5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I95" s="5" t="inlineStr">
+        <is>
+          <t>Xem Swagger/controller để biết DTO và điều kiện chi tiết.</t>
+        </is>
+      </c>
+      <c r="J95" s="5" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/service-categories/{id}</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>Endpoint triển khai trong Swagger</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="inlineStr">
+        <is>
+          <t>Theo vai trò, quyền và phạm vi dữ liệu tại API</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H96" s="5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I96" s="5" t="inlineStr">
+        <is>
+          <t>Xem Swagger/controller để biết DTO và điều kiện chi tiết.</t>
+        </is>
+      </c>
+      <c r="J96" s="5" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>StaffManagement</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/staff/schedules/{id}</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>Endpoint triển khai trong Swagger</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>Theo vai trò, quyền và phạm vi dữ liệu tại API</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I97" s="5" t="inlineStr">
+        <is>
+          <t>Xem Swagger/controller để biết DTO và điều kiện chi tiết.</t>
+        </is>
+      </c>
+      <c r="J97" s="5" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>Administration</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/admin/accounts</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>Endpoint triển khai trong Swagger</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="inlineStr">
+        <is>
+          <t>Theo vai trò, quyền và phạm vi dữ liệu tại API</t>
+        </is>
+      </c>
+      <c r="G98" s="5" t="inlineStr">
+        <is>
+          <t>; query: keyword?</t>
+        </is>
+      </c>
+      <c r="H98" s="5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I98" s="5" t="inlineStr">
+        <is>
+          <t>Xem Swagger/controller để biết DTO và điều kiện chi tiết.</t>
+        </is>
+      </c>
+      <c r="J98" s="5" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>Administration</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/admin/audit-logs</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>Endpoint triển khai trong Swagger</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>Theo vai trò, quyền và phạm vi dữ liệu tại API</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>; query: take?</t>
+        </is>
+      </c>
+      <c r="H99" s="5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I99" s="5" t="inlineStr">
+        <is>
+          <t>Xem Swagger/controller để biết DTO và điều kiện chi tiết.</t>
+        </is>
+      </c>
+      <c r="J99" s="5" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>Administration</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/admin/login-logs</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="inlineStr">
+        <is>
+          <t>Endpoint triển khai trong Swagger</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="inlineStr">
+        <is>
+          <t>Theo vai trò, quyền và phạm vi dữ liệu tại API</t>
+        </is>
+      </c>
+      <c r="G100" s="5" t="inlineStr">
+        <is>
+          <t>; query: take?</t>
+        </is>
+      </c>
+      <c r="H100" s="5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I100" s="5" t="inlineStr">
+        <is>
+          <t>Xem Swagger/controller để biết DTO và điều kiện chi tiết.</t>
+        </is>
+      </c>
+      <c r="J100" s="5" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>Administration</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/admin/permissions</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>Endpoint triển khai trong Swagger</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>Theo vai trò, quyền và phạm vi dữ liệu tại API</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I101" s="5" t="inlineStr">
+        <is>
+          <t>Xem Swagger/controller để biết DTO và điều kiện chi tiết.</t>
+        </is>
+      </c>
+      <c r="J101" s="5" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>Administration</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/admin/roles</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>Endpoint triển khai trong Swagger</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="inlineStr">
+        <is>
+          <t>Theo vai trò, quyền và phạm vi dữ liệu tại API</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H102" s="5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I102" s="5" t="inlineStr">
+        <is>
+          <t>Xem Swagger/controller để biết DTO và điều kiện chi tiết.</t>
+        </is>
+      </c>
+      <c r="J102" s="5" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>Administration</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/admin/roles/{roleId}/permissions</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>Endpoint triển khai trong Swagger</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t>Theo vai trò, quyền và phạm vi dữ liệu tại API</t>
+        </is>
+      </c>
+      <c r="G103" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H103" s="5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I103" s="5" t="inlineStr">
+        <is>
+          <t>Xem Swagger/controller để biết DTO và điều kiện chi tiết.</t>
+        </is>
+      </c>
+      <c r="J103" s="5" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>AppointmentManagement</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/appointments/available-slots</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>Endpoint triển khai trong Swagger</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="inlineStr">
+        <is>
+          <t>Theo vai trò, quyền và phạm vi dữ liệu tại API</t>
+        </is>
+      </c>
+      <c r="G104" s="5" t="inlineStr">
+        <is>
+          <t>; query: date?, staffId?, serviceId?, durationMinutes?</t>
+        </is>
+      </c>
+      <c r="H104" s="5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I104" s="5" t="inlineStr">
+        <is>
+          <t>Xem Swagger/controller để biết DTO và điều kiện chi tiết.</t>
+        </is>
+      </c>
+      <c r="J104" s="5" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>Combos</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/combos</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>Endpoint triển khai trong Swagger</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>Theo vai trò, quyền và phạm vi dữ liệu tại API</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H105" s="5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I105" s="5" t="inlineStr">
+        <is>
+          <t>Xem Swagger/controller để biết DTO và điều kiện chi tiết.</t>
+        </is>
+      </c>
+      <c r="J105" s="5" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>Combos</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/combos/{id}</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="inlineStr">
+        <is>
+          <t>Endpoint triển khai trong Swagger</t>
+        </is>
+      </c>
+      <c r="F106" s="5" t="inlineStr">
+        <is>
+          <t>Theo vai trò, quyền và phạm vi dữ liệu tại API</t>
+        </is>
+      </c>
+      <c r="G106" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H106" s="5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I106" s="5" t="inlineStr">
+        <is>
+          <t>Xem Swagger/controller để biết DTO và điều kiện chi tiết.</t>
+        </is>
+      </c>
+      <c r="J106" s="5" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/customers/me</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>Endpoint triển khai trong Swagger</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>Theo vai trò, quyền và phạm vi dữ liệu tại API</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H107" s="5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I107" s="5" t="inlineStr">
+        <is>
+          <t>Xem Swagger/controller để biết DTO và điều kiện chi tiết.</t>
+        </is>
+      </c>
+      <c r="J107" s="5" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/customers/me/points</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>Endpoint triển khai trong Swagger</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="inlineStr">
+        <is>
+          <t>Theo vai trò, quyền và phạm vi dữ liệu tại API</t>
+        </is>
+      </c>
+      <c r="G108" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H108" s="5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I108" s="5" t="inlineStr">
+        <is>
+          <t>Xem Swagger/controller để biết DTO và điều kiện chi tiết.</t>
+        </is>
+      </c>
+      <c r="J108" s="5" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>CustomerVouchers</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/customers/me/vouchers</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>Endpoint triển khai trong Swagger</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t>Theo vai trò, quyền và phạm vi dữ liệu tại API</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H109" s="5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I109" s="5" t="inlineStr">
+        <is>
+          <t>Xem Swagger/controller để biết DTO và điều kiện chi tiết.</t>
+        </is>
+      </c>
+      <c r="J109" s="5" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>Staff</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/staff/schedules</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t>Endpoint triển khai trong Swagger</t>
+        </is>
+      </c>
+      <c r="F110" s="5" t="inlineStr">
+        <is>
+          <t>Theo vai trò, quyền và phạm vi dữ liệu tại API</t>
+        </is>
+      </c>
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>; query: staffId?, from?, to?</t>
+        </is>
+      </c>
+      <c r="H110" s="5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I110" s="5" t="inlineStr">
+        <is>
+          <t>Xem Swagger/controller để biết DTO và điều kiện chi tiết.</t>
+        </is>
+      </c>
+      <c r="J110" s="5" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>StaffManagement</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/staff/{id}/appointments</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>Endpoint triển khai trong Swagger</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="inlineStr">
+        <is>
+          <t>Theo vai trò, quyền và phạm vi dữ liệu tại API</t>
+        </is>
+      </c>
+      <c r="G111" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H111" s="5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I111" s="5" t="inlineStr">
+        <is>
+          <t>Xem Swagger/controller để biết DTO và điều kiện chi tiết.</t>
+        </is>
+      </c>
+      <c r="J111" s="5" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>Promotions</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/vouchers</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>Endpoint triển khai trong Swagger</t>
+        </is>
+      </c>
+      <c r="F112" s="5" t="inlineStr">
+        <is>
+          <t>Theo vai trò, quyền và phạm vi dữ liệu tại API</t>
+        </is>
+      </c>
+      <c r="G112" s="5" t="inlineStr">
+        <is>
+          <t>; query: keyword?, active?</t>
+        </is>
+      </c>
+      <c r="H112" s="5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I112" s="5" t="inlineStr">
+        <is>
+          <t>Xem Swagger/controller để biết DTO và điều kiện chi tiết.</t>
+        </is>
+      </c>
+      <c r="J112" s="5" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>Administration</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>PATCH</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/admin/accounts/{accountId}/status</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>Endpoint triển khai trong Swagger</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t>Theo vai trò, quyền và phạm vi dữ liệu tại API</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>; query: active?</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I113" s="5" t="inlineStr">
+        <is>
+          <t>Xem Swagger/controller để biết DTO và điều kiện chi tiết.</t>
+        </is>
+      </c>
+      <c r="J113" s="5" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>AppointmentManagement</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>PATCH</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/appointments/{id}/status</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>Endpoint triển khai trong Swagger</t>
+        </is>
+      </c>
+      <c r="F114" s="5" t="inlineStr">
+        <is>
+          <t>Theo vai trò, quyền và phạm vi dữ liệu tại API</t>
+        </is>
+      </c>
+      <c r="G114" s="5" t="inlineStr">
+        <is>
+          <t>body: AppointmentStatusRequest</t>
+        </is>
+      </c>
+      <c r="H114" s="5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I114" s="5" t="inlineStr">
+        <is>
+          <t>Xem Swagger/controller để biết DTO và điều kiện chi tiết.</t>
+        </is>
+      </c>
+      <c r="J114" s="5" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>Promotions</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>PATCH</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/promotions/vouchers/{id}/status</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>Endpoint triển khai trong Swagger</t>
+        </is>
+      </c>
+      <c r="F115" s="5" t="inlineStr">
+        <is>
+          <t>Theo vai trò, quyền và phạm vi dữ liệu tại API</t>
+        </is>
+      </c>
+      <c r="G115" s="5" t="inlineStr">
+        <is>
+          <t>; query: active?</t>
+        </is>
+      </c>
+      <c r="H115" s="5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I115" s="5" t="inlineStr">
+        <is>
+          <t>Xem Swagger/controller để biết DTO và điều kiện chi tiết.</t>
+        </is>
+      </c>
+      <c r="J115" s="5" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>Reviews</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>PATCH</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/reviews/{id}/moderation</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="inlineStr">
+        <is>
+          <t>Endpoint triển khai trong Swagger</t>
+        </is>
+      </c>
+      <c r="F116" s="5" t="inlineStr">
+        <is>
+          <t>Theo vai trò, quyền và phạm vi dữ liệu tại API</t>
+        </is>
+      </c>
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>; query: visible?</t>
+        </is>
+      </c>
+      <c r="H116" s="5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I116" s="5" t="inlineStr">
+        <is>
+          <t>Xem Swagger/controller để biết DTO và điều kiện chi tiết.</t>
+        </is>
+      </c>
+      <c r="J116" s="5" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>Combos</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/combos</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>Endpoint triển khai trong Swagger</t>
+        </is>
+      </c>
+      <c r="F117" s="5" t="inlineStr">
+        <is>
+          <t>Theo vai trò, quyền và phạm vi dữ liệu tại API</t>
+        </is>
+      </c>
+      <c r="G117" s="5" t="inlineStr">
+        <is>
+          <t>body: ComboRequest</t>
+        </is>
+      </c>
+      <c r="H117" s="5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I117" s="5" t="inlineStr">
+        <is>
+          <t>Xem Swagger/controller để biết DTO và điều kiện chi tiết.</t>
+        </is>
+      </c>
+      <c r="J117" s="5" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>Promotions</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/promotions/vouchers</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="inlineStr">
+        <is>
+          <t>Endpoint triển khai trong Swagger</t>
+        </is>
+      </c>
+      <c r="F118" s="5" t="inlineStr">
+        <is>
+          <t>Theo vai trò, quyền và phạm vi dữ liệu tại API</t>
+        </is>
+      </c>
+      <c r="G118" s="5" t="inlineStr">
+        <is>
+          <t>body: VoucherRequest</t>
+        </is>
+      </c>
+      <c r="H118" s="5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I118" s="5" t="inlineStr">
+        <is>
+          <t>Xem Swagger/controller để biết DTO và điều kiện chi tiết.</t>
+        </is>
+      </c>
+      <c r="J118" s="5" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>Promotions</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/promotions/vouchers/validate</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>Endpoint triển khai trong Swagger</t>
+        </is>
+      </c>
+      <c r="F119" s="5" t="inlineStr">
+        <is>
+          <t>Theo vai trò, quyền và phạm vi dữ liệu tại API</t>
+        </is>
+      </c>
+      <c r="G119" s="5" t="inlineStr">
+        <is>
+          <t>; query: code?</t>
+        </is>
+      </c>
+      <c r="H119" s="5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I119" s="5" t="inlineStr">
+        <is>
+          <t>Xem Swagger/controller để biết DTO và điều kiện chi tiết.</t>
+        </is>
+      </c>
+      <c r="J119" s="5" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>Reviews</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/reviews/invoices/{invoiceId}</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>Endpoint triển khai trong Swagger</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="inlineStr">
+        <is>
+          <t>Theo vai trò, quyền và phạm vi dữ liệu tại API</t>
+        </is>
+      </c>
+      <c r="G120" s="5" t="inlineStr">
+        <is>
+          <t>body: ReviewRequest</t>
+        </is>
+      </c>
+      <c r="H120" s="5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I120" s="5" t="inlineStr">
+        <is>
+          <t>Xem Swagger/controller để biết DTO và điều kiện chi tiết.</t>
+        </is>
+      </c>
+      <c r="J120" s="5" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>Staff</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/staff/schedules</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>Endpoint triển khai trong Swagger</t>
+        </is>
+      </c>
+      <c r="F121" s="5" t="inlineStr">
+        <is>
+          <t>Theo vai trò, quyền và phạm vi dữ liệu tại API</t>
+        </is>
+      </c>
+      <c r="G121" s="5" t="inlineStr">
+        <is>
+          <t>body: WorkScheduleRequest</t>
+        </is>
+      </c>
+      <c r="H121" s="5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I121" s="5" t="inlineStr">
+        <is>
+          <t>Xem Swagger/controller để biết DTO và điều kiện chi tiết.</t>
+        </is>
+      </c>
+      <c r="J121" s="5" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>Administration</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/admin/roles/{roleId}/permissions/{permissionId}</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="inlineStr">
+        <is>
+          <t>Endpoint triển khai trong Swagger</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="inlineStr">
+        <is>
+          <t>Theo vai trò, quyền và phạm vi dữ liệu tại API</t>
+        </is>
+      </c>
+      <c r="G122" s="5" t="inlineStr">
+        <is>
+          <t>body: RolePermissionRequest</t>
+        </is>
+      </c>
+      <c r="H122" s="5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I122" s="5" t="inlineStr">
+        <is>
+          <t>Xem Swagger/controller để biết DTO và điều kiện chi tiết.</t>
+        </is>
+      </c>
+      <c r="J122" s="5" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>Combos</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/combos/{id}</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>Endpoint triển khai trong Swagger</t>
+        </is>
+      </c>
+      <c r="F123" s="5" t="inlineStr">
+        <is>
+          <t>Theo vai trò, quyền và phạm vi dữ liệu tại API</t>
+        </is>
+      </c>
+      <c r="G123" s="5" t="inlineStr">
+        <is>
+          <t>body: ComboRequest</t>
+        </is>
+      </c>
+      <c r="H123" s="5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I123" s="5" t="inlineStr">
+        <is>
+          <t>Xem Swagger/controller để biết DTO và điều kiện chi tiết.</t>
+        </is>
+      </c>
+      <c r="J123" s="5" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/customers/me</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t>Endpoint triển khai trong Swagger</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>Theo vai trò, quyền và phạm vi dữ liệu tại API</t>
+        </is>
+      </c>
+      <c r="G124" s="5" t="inlineStr">
+        <is>
+          <t>body: UpdateCustomerRequest</t>
+        </is>
+      </c>
+      <c r="H124" s="5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I124" s="5" t="inlineStr">
+        <is>
+          <t>Xem Swagger/controller để biết DTO và điều kiện chi tiết.</t>
+        </is>
+      </c>
+      <c r="J124" s="5" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>Promotions</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/promotions/vouchers/{id}</t>
+        </is>
+      </c>
+      <c r="E125" s="5" t="inlineStr">
+        <is>
+          <t>Endpoint triển khai trong Swagger</t>
+        </is>
+      </c>
+      <c r="F125" s="5" t="inlineStr">
+        <is>
+          <t>Theo vai trò, quyền và phạm vi dữ liệu tại API</t>
+        </is>
+      </c>
+      <c r="G125" s="5" t="inlineStr">
+        <is>
+          <t>body: VoucherRequest</t>
+        </is>
+      </c>
+      <c r="H125" s="5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I125" s="5" t="inlineStr">
+        <is>
+          <t>Xem Swagger/controller để biết DTO và điều kiện chi tiết.</t>
+        </is>
+      </c>
+      <c r="J125" s="5" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>StaffManagement</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/staff/schedules/{id}</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="inlineStr">
+        <is>
+          <t>Endpoint triển khai trong Swagger</t>
+        </is>
+      </c>
+      <c r="F126" s="5" t="inlineStr">
+        <is>
+          <t>Theo vai trò, quyền và phạm vi dữ liệu tại API</t>
+        </is>
+      </c>
+      <c r="G126" s="5" t="inlineStr">
+        <is>
+          <t>body: WorkScheduleRequest</t>
+        </is>
+      </c>
+      <c r="H126" s="5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I126" s="5" t="inlineStr">
+        <is>
+          <t>Xem Swagger/controller để biết DTO và điều kiện chi tiết.</t>
+        </is>
+      </c>
+      <c r="J126" s="5" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I86"/>
+  <autoFilter ref="A1:J126"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/KLCN021_API_Catalog.xlsx
+++ b/KLCN021_API_Catalog.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conventions" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'API Catalog'!$A$1:$J$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'API Catalog'!$A$1:$J$133</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J126"/>
+  <dimension ref="A1:J133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="6" customWidth="1" style="4" min="1" max="1"/>
@@ -776,7 +776,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Auth</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Yêu cầu đặt lại mật khẩu</t>
+          <t>Yêu cầu OTP khôi phục mật khẩu</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Anonymous + IP rate limit</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -806,13 +806,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>204 No Content</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="n"/>
+          <t>200 {message}; không trả debugOtp</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Generic cho email tồn tại/không tồn tại; OTP15phút, gửi lại60giây,5lần/giờ/tài khoản; IP10lần/10phút.</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Chưa có trong Swagger hiện tại</t>
+          <t>Đã triển khai</t>
         </is>
       </c>
     </row>
@@ -2502,12 +2506,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>{ items: AppointmentResponse[], totalCount, page, pageSize }</t>
+          <t>{items:AppointmentResponse[],totalCount,page,pageSize}; items add invoiceId,invoiceStatus,hasReviewed,reviewStars</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Management APPOINTMENT.READ sees all; Staff APPOINTMENT.READ assigned only; Customer own records.</t>
+          <t>Management APPOINTMENT.READ sees all; Staff APPOINTMENT.READ assigned only; Customer own records. Latest invoice by date/ID descending; hidden review still reviewed. Missing invoice: null metadata, false reviewed.</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -3544,20 +3548,24 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Public/Admin</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>serviceId?, rating?, page, size</t>
+          <t>serviceId? (positive integer)</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>PagedResult&lt;DanhGiaDto&gt;</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="n"/>
+          <t>{averageRating, totalReviews, items:[{danhGiaId,hoaDonId,soSao,binhLuan,ngayDanhGia,tenKhachHang}]}</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>Visible only; direct/combo services. Full-set statistics, max200 recent items. Empty average0. Response changed from array: clients read items.</t>
+        </is>
+      </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
           <t>Đã triển khai</t>
@@ -3631,28 +3639,32 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Danh sách thông báo</t>
+          <t>Hộp thư thông báo của khách hàng</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Authenticated</t>
+          <t>Authenticated account with customer profile</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>unreadOnly, page, size</t>
+          <t>page=1,pageSize=20(max100),unreadOnly=false</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>PagedResult&lt;ThongBaoDto&gt;</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="n"/>
+          <t>200 {items:[{id,title,body,type,data,isRead,createdAt}],totalCount,unreadCount,page,pageSize}</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Own private + broadcasts; per-account read state; data is JSON string; UTC timestamp. Missing auth401; no customer403. Requires migration06.</t>
+        </is>
+      </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>Chưa có trong Swagger hiện tại</t>
+          <t>Đã triển khai</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4684,7 @@
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>Admin/Manager + REVIEW.MODERATE</t>
+          <t>Admin/Manager/Reception + REVIEW.MODERATE</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
@@ -6022,22 +6034,22 @@
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>Theo vai trò, quyền và phạm vi dữ liệu tại API</t>
+          <t>Admin/Manager/Reception + REVIEW.MODERATE</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr">
         <is>
-          <t>; query: visible?</t>
+          <t>query visible (boolean)</t>
         </is>
       </c>
       <c r="H116" s="5" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>204 No Content</t>
         </is>
       </c>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>Xem Swagger/controller để biết DTO và điều kiện chi tiết.</t>
+          <t>false=An, true=HienThi; 404 missing review.</t>
         </is>
       </c>
       <c r="J116" s="5" t="inlineStr">
@@ -6217,27 +6229,27 @@
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>Endpoint triển khai trong Swagger</t>
+          <t>Review owned paid invoice; visible immediately</t>
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>Theo vai trò, quyền và phạm vi dữ liệu tại API</t>
+          <t>Authenticated customer, invoice owner</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
         <is>
-          <t>body: ReviewRequest</t>
+          <t>stars (1..5), comment? (max1000)</t>
         </is>
       </c>
       <c r="H120" s="5" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>201 {danhGiaId,hoaDonId,soSao,binhLuan,trangThai,ngayDanhGia}</t>
         </is>
       </c>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>Xem Swagger/controller để biết DTO và điều kiện chi tiết.</t>
+          <t>HienThi by default; unpaid400, not owner404, duplicate409 including concurrent requests. Requires migration05.</t>
         </is>
       </c>
       <c r="J120" s="5" t="inlineStr">
@@ -6546,8 +6558,358 @@
         </is>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>/api/v1/auth/reset-password</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Xác nhận OTP và đặt mật khẩu mới</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Anonymous + IP rate limit</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>email, otp (chuỗi6số), newPassword (8–128)</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>200 {message}; không tự đăng nhập</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>OTP1lần/5lượt thử;400sai/hết hạn/đã dùng;429IP20lần/10phút; resetSecurityStamp+revokeallrefresh+audit.</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Reviews</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>/api/v1/reviews/appointments/{appointmentId}</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Review owned completed appointment</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Authenticated customer, appointment owner</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>stars (1..5), comment? (max1000)</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>201 review summary; HienThi</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Latest invoice must be paid; invalid/incomplete/unpaid400, not owner404, duplicate409. Same uniqueness as invoice route.</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>/api/v1/notifications/device-token</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Đăng ký hoặc cập nhật token FCM</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Authenticated account with customer profile</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>{token (max500,no whitespace),deviceType:android|ios|web}</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>200 {message}</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Token unique and case-sensitive; rebind to current account/customer. Invalid400. Missing auth401; no customer403. Requires migration06.</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>/api/v1/notifications/device-token</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Hủy token trước khi đăng xuất</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Authenticated account with customer profile</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>query token (URL encoded)</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>204 No Content</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Owner-qualified update; idempotent; cannot disable token rebound to another account. Missing auth401; no customer403. Requires migration06.</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>/api/v1/notifications/unread-count</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Đếm thông báo chưa đọc</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Authenticated account with customer profile</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>200 {unreadCount}</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Counts own private and global notifications; independent per account. Missing auth401; no customer403. Requires migration06.</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>PATCH</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>/api/v1/notifications/{id}/read</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Đánh dấu một thông báo đã đọc</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Authenticated account with customer profile</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>204 No Content</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Own inbox only; inaccessible404; duplicate read idempotent. Missing auth401; no customer403. Requires migration06.</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>PATCH</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>/api/v1/notifications/read-all</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Đánh dấu hộp thư hiện tại đã đọc</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Authenticated account with customer profile</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>204 No Content</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Per-account receipt snapshot; other customers unaffected. Missing auth401; no customer403. Requires migration06.</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J126"/>
+  <autoFilter ref="A1:J133"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6558,7 +6920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="18" customWidth="1" style="4" min="1" max="1"/>
@@ -6886,6 +7248,57 @@
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>POST/GET appointment list; decimal money is retained. Detail/reschedule still use existing entity-shaped JSON.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>DeviceTokenRequest</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>token, deviceType</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>POST /notifications/device-token</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>NotificationResponse</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>id,title,body,type,data:string?,isRead,createdAt UTC</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>GET /notifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ThongBaoDaDoc</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>thongBaoId,taiKhoanId,ngayDoc (composite key)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Per-account read receipts; shared broadcast remains unread for other customers</t>
         </is>
       </c>
     </row>
@@ -6900,7 +7313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="13" customWidth="1" style="4" min="1" max="1"/>
@@ -7053,6 +7466,18 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Notifications (2026-10-17)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>06migration adds3tables + appointment/invoice rowversion; total28business tables. Durable push outbox; Firebase default disabled; per-account broadcast reads. Vietnamese handoff REVIEWS.md section11.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/KLCN021_API_Catalog.xlsx
+++ b/KLCN021_API_Catalog.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conventions" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'API Catalog'!$A$1:$J$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'API Catalog'!$A$1:$J$136</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J133"/>
+  <dimension ref="A1:J144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="6" customWidth="1" style="4" min="1" max="1"/>
@@ -1747,28 +1747,32 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Xem điểm thưởng/lịch sử điểm</t>
+          <t>Lịch sử điểm của khách cho quản trị</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Admin/Reception/Owner</t>
+          <t>Admin/Manager/Reception + CUSTOMER.READ</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>page, size</t>
+          <t>page=1,pageSize=20(1..100)</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>PointBalance + giaoDichDiem[]</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="n"/>
+          <t>{customerId,diemThuong,transactions,totalCount,page,pageSize}</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Transactions include invoiceId/voucherId links;404 missing;400 invalidpagination.</t>
+        </is>
+      </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Chưa có trong Swagger hiện tại</t>
+          <t>Đã triển khai</t>
         </is>
       </c>
     </row>
@@ -1946,7 +1950,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>PagedResult&lt;DichVuDto&gt;</t>
+          <t>PagedResult&lt;DichVuDto&gt;; includes imageUrl nullable</t>
         </is>
       </c>
       <c r="I31" s="2" t="n"/>
@@ -1987,12 +1991,12 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>loaiDichVuId, tenDichVu, gia, thoiLuong, moTa</t>
+          <t>loaiDichVuId, tenDichVu, gia, thoiLuong, moTa; imageUrl? (HTTP/S,max2048; update null preserves, empty clears)</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>DichVuDto</t>
+          <t>DichVuDto; includes imageUrl nullable</t>
         </is>
       </c>
       <c r="I32" s="2" t="n"/>
@@ -2038,7 +2042,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>DichVuDetailDto</t>
+          <t>DichVuDetailDto; includes imageUrl nullable</t>
         </is>
       </c>
       <c r="I33" s="2" t="n"/>
@@ -2079,12 +2083,12 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>DichVu fields</t>
+          <t>DichVu fields; imageUrl? (HTTP/S,max2048; update null preserves, empty clears)</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>DichVuDto</t>
+          <t>DichVuDto; includes imageUrl nullable</t>
         </is>
       </c>
       <c r="I34" s="2" t="n"/>
@@ -2807,7 +2811,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Completed/matching booked lines required. Whole redeemed points clamp to actual discount; ledger references invoice. Management also INVOICE.WRITE.</t>
+          <t>Completed/matching booked lines required. Whole redeemed points clamp to actual discount; ledger references invoice. Management also INVOICE.WRITE. Unique perappointment; customer/voucherconcurrency409; unclaimedpointvoucher400.</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -3558,12 +3562,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>{averageRating, totalReviews, items:[{danhGiaId,hoaDonId,soSao,binhLuan,ngayDanhGia,tenKhachHang}]}</t>
+          <t>{averageRating,totalReviews,items:[{danhGiaId,hoaDonId,soSao,binhLuan,ngayDanhGia,tenKhachHang,reply,repliedAt}]}</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>Visible only; direct/combo services. Full-set statistics, max200 recent items. Empty average0. Response changed from array: clients read items.</t>
+          <t>Visible non-deleted reviews only; full-set statistics, max200 latest. Read items envelope. Reply author account remains private. Requires SQL11.</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -3735,28 +3739,32 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Báo cáo lịch hẹn</t>
+          <t>Legacy appointment status totals</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>REPORT.READ + existing role allowlist</t>
+          <t>Admin/Manager/Reception + REPORT.READ</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>from, to, groupBy, status?</t>
+          <t>from?,to? (inclusive/exclusive)</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>ReportResult</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="n"/>
+          <t>[{status,count}]</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Backward-compatible status totals; use appointment-summary for day/week/month.</t>
+        </is>
+      </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>Đã triển khai</t>
+          <t>Implemented</t>
         </is>
       </c>
     </row>
@@ -3781,28 +3789,32 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Báo cáo doanh thu</t>
+          <t>Legacy paid invoice summary</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>REPORT.READ + existing role allowlist</t>
+          <t>Admin/Manager/Reception + REPORT.READ</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>from, to, groupBy, type?</t>
+          <t>from?,to? (inclusive/exclusive)</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>RevenueReport</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="n"/>
+          <t>{invoiceCount,revenue}</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Paid invoices only by invoice creation date; use order-summary for time periods.</t>
+        </is>
+      </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>Đã triển khai</t>
+          <t>Implemented</t>
         </is>
       </c>
     </row>
@@ -3827,28 +3839,32 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Báo cáo khách hàng</t>
+          <t>Legacy top customers</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>REPORT.READ + existing role allowlist</t>
+          <t>Admin/Manager/Reception + REPORT.READ</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>from, to, segment?</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>CustomerReport</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="n"/>
+          <t>CustomerReport[] (max200)</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>Not a total customer count or new-customer report. Use new-customers.</t>
+        </is>
+      </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>Đã triển khai</t>
+          <t>Implemented</t>
         </is>
       </c>
     </row>
@@ -3873,28 +3889,32 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Báo cáo dịch vụ/combo/nhân viên</t>
+          <t>Legacy paid service/combo sales</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>REPORT.READ + existing role allowlist</t>
+          <t>Admin/Manager/Reception + REPORT.READ</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>from, to, serviceId?, staffId?</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>ServiceReport</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="n"/>
+          <t>[{dichVuId,name,quantity,revenue}]</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>All-time paid gross line sales. Combo identity distinct internally, legacy response shape retained. Use order-breakdown for explicit IDs and filters.</t>
+        </is>
+      </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>Đã triển khai</t>
+          <t>Implemented</t>
         </is>
       </c>
     </row>
@@ -3919,28 +3939,32 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Xuất báo cáo Excel/PDF</t>
+          <t>Export report as genuine Excel XLSX</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>REPORT.READ + existing role allowlist</t>
+          <t>Admin/Manager/Reception + REPORT.READ</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>reportType, from, to, format</t>
+          <t>report=appointments|orders|breakdown|new-customers; report filters</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>File stream</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="n"/>
+          <t>XLSX file</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>REPORT.READ. Max10000 rows including metadata; filter before export. Orders export is time summary. PDF via existing Web browser print only; no PDF API. SQL12 prepared, not applied locally: SSPI blocked live verification.</t>
+        </is>
+      </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>Chưa có trong Swagger hiện tại</t>
+          <t>Implemented</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5518,7 @@
       </c>
       <c r="H105" s="5" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>200; includes imageUrl nullable</t>
         </is>
       </c>
       <c r="I105" s="5" t="inlineStr">
@@ -5544,7 +5568,7 @@
       </c>
       <c r="H106" s="5" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>200; includes imageUrl nullable</t>
         </is>
       </c>
       <c r="I106" s="5" t="inlineStr">
@@ -6049,7 +6073,7 @@
       </c>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>false=An, true=HienThi; 404 missing review.</t>
+          <t>false=An, true=HienThi. Deleted/missing404; concurrent change409. REVIEW.MODERATE; SQL11.</t>
         </is>
       </c>
       <c r="J116" s="5" t="inlineStr">
@@ -6089,12 +6113,12 @@
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>body: ComboRequest</t>
+          <t>body: ComboRequest; imageUrl? (HTTP/S,max2048; update null preserves, empty clears)</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>200; includes imageUrl nullable</t>
         </is>
       </c>
       <c r="I117" s="5" t="inlineStr">
@@ -6139,7 +6163,7 @@
       </c>
       <c r="G118" s="5" t="inlineStr">
         <is>
-          <t>body: VoucherRequest</t>
+          <t>body: VoucherRequest; pointsCost=0 (0..1000000)</t>
         </is>
       </c>
       <c r="H118" s="5" t="inlineStr">
@@ -6149,7 +6173,7 @@
       </c>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>Xem Swagger/controller để biết DTO và điều kiện chi tiết.</t>
+          <t>Positive pointsCost requires unassigned offer; redeemed owner/cost immutable; used voucher cannotreactivate. RowVersionconflict409.</t>
         </is>
       </c>
       <c r="J118" s="5" t="inlineStr">
@@ -6389,12 +6413,12 @@
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>body: ComboRequest</t>
+          <t>body: ComboRequest; imageUrl? (HTTP/S,max2048; update null preserves, empty clears)</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>200; includes imageUrl nullable</t>
         </is>
       </c>
       <c r="I123" s="5" t="inlineStr">
@@ -6489,7 +6513,7 @@
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>body: VoucherRequest</t>
+          <t>body: VoucherRequest; pointsCost=0 (0..1000000)</t>
         </is>
       </c>
       <c r="H125" s="5" t="inlineStr">
@@ -6499,7 +6523,7 @@
       </c>
       <c r="I125" s="5" t="inlineStr">
         <is>
-          <t>Xem Swagger/controller để biết DTO và điều kiện chi tiết.</t>
+          <t>Positive pointsCost requires unassigned offer; redeemed owner/cost immutable; used voucher cannotreactivate. RowVersionconflict409.</t>
         </is>
       </c>
       <c r="J125" s="5" t="inlineStr">
@@ -6908,8 +6932,558 @@
         </is>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>/api/v1/media/images</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Upload ảnh dịch vụ/combo lên Cloudinary</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Admin/Manager/Reception + SERVICE.WRITE</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>multipart/form-data field file, PNG/JPEG/WebP &lt;=5MiB</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>201 {imageUrl,publicId}</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>400 invalid file;413 oversize;503 unconfigured;502 provider;504 timeout. Save returned imageUrl in service/combo POST/PUT.</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>/api/v1/customers/me/voucher-offers</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Danh sách voucher đổi điểm chưa nhận</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Authenticated customer profile</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>[{id,promotionId,promotionName,discountValue,expiresAt,pointsCost}]</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Codes redacted; unassigned/unredeemed/unused active offers only.403 no profile.</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>/api/v1/customers/me/vouchers/{id}/redeem</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Đổi điểm lấy một mã voucher</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Authenticated customer profile</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>No body</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>200 {voucherId,code,pointsSpent,remainingPoints}</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Atomic balance/ownership/ledger;400 insufficient;403 no profile;404 invalid;409 claimed/concurrent. No double charge on invoice use.</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Đã triển khai</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Reviews</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>/api/v1/reviews/management</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Management list and filters</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Admin/Manager/Reception + REVIEW.MODERATE</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>serviceId?, from?, to?, stars? (1..5), status? (HienThi/ChoDuyet/An), page=1,pageSize=20 (max100)</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>200 {items,totalCount,averageRating,page,pageSize}</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Includes hidden/pending, customer/service/combo details and saved reply. Excludes soft-deleted. Date boundaries inclusive; use explicit date-time. SQL11.</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Reviews</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>/api/v1/reviews/{id}/reply</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Create or replace staff reply</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Admin/Manager/Reception + REVIEW.MODERATE</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>JSON {reply: string (1..2000, nonblank)}</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>204 No Content</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Reply saved in database, returned by public visible review list. Deleted/missing404; concurrency409. No automatic push/email. SQL11.</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Reviews</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>/api/v1/reviews/{id}</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Soft-delete violating review</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Admin/Manager/Reception + REVIEW.MODERATE</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>204 No Content</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Preserves original review/invoice uniqueness and hasReviewed; public/pending/management exclude deleted. Cannot revive via moderation. Missing/deleted404; concurrent409. SQL11.</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Reports</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>/api/v1/reports/appointment-summary</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Appointment counts by period/status</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Admin/Manager/Reception + REPORT.READ</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>groupBy=day|week|month|status; from?,to?,status?,staffId?,serviceId?,comboId?,categoryId?,search?</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>{totalCount,items:[{periodStart,status,count}]}</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Date range [from,to); Monday weeks; appointment time. Max100000 source rows; overflow400.</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Reports</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>/api/v1/reports/orders</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Search and paginate service invoices</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Admin/Manager/Reception + REPORT.READ</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>from?,to?,status?,staffId?,serviceId?,comboId?,categoryId?,search?,page=1,pageSize=20 (max100)</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>{totalCount,paidRevenue,page,pageSize,items}</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Invoice creation dates; counts all matching statuses, paidRevenue only settled invoices. Item gross/net distinguished.</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Reports</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>/api/v1/reports/order-summary</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Invoice counts by day/week/month/quarter/year</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Admin/Manager/Reception + REPORT.READ</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>groupBy=day|week|month|quarter|year; invoice filters</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>{totalCount,paidRevenue,items:[{periodStart,invoiceCount,paidInvoiceCount,unpaidInvoiceCount,paidRevenue}]}</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Defaults groupBy month. Date range [from,to); no partial truncation. Not a payment settlement-date cashflow report.</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Reports</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>/api/v1/reports/order-breakdown</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Invoice breakdown by service/combo/staff/category</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Admin/Manager/Reception + REPORT.READ</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>groupBy=service|combo|staff|category; invoice filters</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>{totalCount,paidRevenue,metric,items}</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Staff: invoiceNet once per invoice. Service/combo/category: lineGrossBeforeDiscount, no invented net allocation; combos category bucket comboUnallocated. Direct-service/category filters exclude combo components.</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Reports</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>/api/v1/reports/new-customers</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>New customer counts by creation period</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Admin/Manager/Reception + REPORT.READ</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>groupBy=day|week|month|quarter|year; from?,to?,search?</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>{totalCount,unknownHistoricalCount,items:[{periodStart,count}]}</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>SQL12 adds nullable CreatedAt default for future registrations. Existing unknown dates remain NULL and excluded from period counts, reported separately. Nonapplicable filters400. SQL12 prepared, not applied locally: SSPI blocked live verification.</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J133"/>
+  <autoFilter ref="A1:J136"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6920,7 +7494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="18" customWidth="1" style="4" min="1" max="1"/>
@@ -7299,6 +7873,40 @@
       <c r="C22" t="inlineStr">
         <is>
           <t>Per-account read receipts; shared broadcast remains unread for other customers</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>UploadImageResponse</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>imageUrl, publicId</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>POST /media/images</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Voucher point exchange</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>pointsCost,redeemedAt,usedAt; ledger voucherId</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>customers/me/voucher-offers; customers/me/vouchers/{id}/redeem</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="13" customWidth="1" style="4" min="1" max="1"/>
@@ -7478,6 +8086,18 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Cloudinary/reminders/points (2026-10-18)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SQL07..10 additive; images storedasURL; reminder60minutes/dedup; pointsCostexchangeatomic; 28tables unchanged. ShortWebhandoff BAO_CAO_5_CHUC_NANG_WEB.md.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/KLCN021_API_Catalog.xlsx
+++ b/KLCN021_API_Catalog.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J144"/>
+  <dimension ref="A1:J156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="6" customWidth="1" style="4" min="1" max="1"/>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Transactions include invoiceId/voucherId links;404 missing;400 invalidpagination.</t>
+          <t>Transactions include invoiceId/voucherId links;404 missing;400 invalidpagination. Transactions append customerPackageId for prepaid purchase reward source.</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>appointmentAt, items[{serviceId, comboId?, expectedPrice}], note?, customerId?, staffId?</t>
+          <t>appointmentAt, items[{serviceId, comboId?, expectedPrice}], note?, customerId?, staffId?; customerPackageId? (purchased package ID)</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Catalog-derived expectedPrice; complete active combo composition/date required. Management also APPOINTMENT.WRITE. Invalid service/combo/shift400; overlap409.</t>
+          <t>Catalog-derived expectedPrice; complete active combo composition/date required. Management also APPOINTMENT.WRITE. Invalid service/combo/shift400; overlap409. Package-funded all-covered ordinary services only; reserved atomically; response customerPackageId/fundingSource.</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -7479,6 +7479,606 @@
       <c r="J144" t="inlineStr">
         <is>
           <t>Implemented</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>ServicePackages</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>/api/v1/service-packages</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>List active service packages</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>ServicePackage[] with items[{id,servicePackageId,serviceId,sessions}]</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Active catalog only; includeInactive=true400.</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Implemented; SQL-backed HTTP smoke verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>ServicePackages</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>/api/v1/service-packages/{id}</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Get active package detail</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>ServicePackage with items</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Inactive or missing404.</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Implemented; SQL-backed HTTP smoke verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>ServicePackages</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>/api/v1/service-packages/management</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Manage complete package catalog</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Admin/Manager/Reception + SERVICE.WRITE</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>ServicePackage[] with items</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Includes inactive.</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Implemented; SQL-backed HTTP smoke verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>ServicePackages</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>/api/v1/service-packages</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Create package catalog entry</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Admin/Manager/Reception + SERVICE.WRITE</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>{name,price,validityDays,items:[{serviceId,sessions}],active=true,imageUrl?}</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>201 ServicePackage</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>No duplicate services;1..100items,1..10000sessions,price0.01..1e9 max2decimals,validity1..3650days. SQL13.</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Implemented; SQL-backed HTTP smoke verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>ServicePackages</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>/api/v1/service-packages/{id}</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Update or deactivate package</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Admin/Manager/Reception + SERVICE.WRITE</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Full ServicePackageRequest</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>200 ServicePackage</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Paid purchase snapshots unchanged; Active=false stops new sales, not existing entitlements. Omitted/null image keeps, empty clears.409concurrency.</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Implemented; SQL-backed HTTP smoke verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>ServicePackages</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>/api/v1/service-packages/purchases</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Create immutable package purchase snapshot</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Customer owner; management + CUSTOMER.WRITE</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>{packageId,customerId?}</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>201 CustomerPackageView Pending</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Management requires customerId; customer cannot buy for another. Pending available0.</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Implemented; SQL-backed HTTP smoke verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>ServicePackages</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>/api/v1/service-packages/purchases/{id}/pay</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Confirm full package payment</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Admin/Manager/Reception + PAYMENT.WRITE</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>{method: TienMat|ChuyenKhoan|The}</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>200 CustomerPackageView Paid</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Server snapshotprice; one payment, starts expiry, earns floor(price/10000) points once;409retry/conflict. Manual received-payment record, not bank gateway.</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Implemented; SQL-backed HTTP smoke verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>ServicePackages</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>/api/v1/service-packages/mine</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>View own packages and session balances</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Authenticated customer profile</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>CustomerPackageView[]</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Per-service granted/reserved/used/remaining/available; expiry or unpaid availability0.</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Implemented; SQL-backed HTTP smoke verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>ServicePackages</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>/api/v1/service-packages/customers/{customerId}</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>View customer purchased packages</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Admin/Manager/Reception + CUSTOMER.READ</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>customerId</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>CustomerPackageView[]</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Purchase snapshots retained after catalog edits.</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Implemented; SQL-backed HTTP smoke verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>ServicePackages</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>/api/v1/service-packages/purchases/{id}</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>View package and usage history</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Customer owner; management + CUSTOMER.READ</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>{package:CustomerPackageView,history:[{id,customerPackageItemId,appointmentId,quantity,status,createdAt,settledAt}]}</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>History Reserved/Consumed/Released. Other customer403.</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Implemented; SQL-backed HTTP smoke verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>ServicePackages</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>/api/v1/service-packages/purchases/{id}</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Cancel pending package purchase</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Customer owner; management + CUSTOMER.WRITE</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>204 No Content</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Paid package cannot cancel/refund here409.</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Implemented; SQL-backed HTTP smoke verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>ServicePackages</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>/api/v1/service-packages/sales</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Report received package purchase income</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Admin/Manager/Reception + REPORT.READ</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>from,to required [from,to), max366days</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>{from,to,count,revenue,items:[{id,customerId,name,price,paidAt,paymentMethod}]}</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>PaidAt basis, separate ordinary invoice revenue; max10000receipts else400.</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>Implemented; SQL-backed HTTP smoke verified</t>
         </is>
       </c>
     </row>
@@ -7494,7 +8094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="18" customWidth="1" style="4" min="1" max="1"/>
@@ -7907,6 +8507,23 @@
       <c r="C24" t="inlineStr">
         <is>
           <t>customers/me/voucher-offers; customers/me/vouchers/{id}/redeem</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ServicePackage/CustomerPackage</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SQL13:5 package tables</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Catalog plus purchase snapshot,per-service entitlements and usage history. Remaining=granted-used;available=remaining-reserved only paid/unexpired.</t>
         </is>
       </c>
     </row>
@@ -7921,7 +8538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="13" customWidth="1" style="4" min="1" max="1"/>
@@ -8098,6 +8715,18 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Prepaid package revenue</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Package receipt records income once; redemption auto paid zero invoice for reviews, no second points/payment. See HUONG_DAN_GOI_DICH_VU.md. Migrations applied by user; SQL-backed HTTP checks pass, SQL write concurrency unverified.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
